--- a/docs/Main-Lab/DownloadContent/WbxOne2026PodDetails.xlsx
+++ b/docs/Main-Lab/DownloadContent/WbxOne2026PodDetails.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bomcgoni/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56E835E1-4065-F849-B7BF-E66FDF24C5D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B6B37C-5DBF-5842-AFC5-81357D68C237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51200" yWindow="620" windowWidth="67720" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="33500" windowHeight="21660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -448,113 +448,113 @@
     <t>Workspace</t>
   </si>
   <si>
-    <t>workspace01</t>
-  </si>
-  <si>
-    <t>workspace02</t>
-  </si>
-  <si>
-    <t>workspace03</t>
-  </si>
-  <si>
-    <t>workspace04</t>
-  </si>
-  <si>
-    <t>workspace05</t>
-  </si>
-  <si>
-    <t>workspace06</t>
-  </si>
-  <si>
-    <t>workspace07</t>
-  </si>
-  <si>
-    <t>workspace08</t>
-  </si>
-  <si>
-    <t>workspace09</t>
-  </si>
-  <si>
-    <t>workspace10</t>
-  </si>
-  <si>
-    <t>workspace11</t>
-  </si>
-  <si>
-    <t>workspace12</t>
-  </si>
-  <si>
-    <t>workspace13</t>
-  </si>
-  <si>
-    <t>workspace14</t>
-  </si>
-  <si>
-    <t>workspace15</t>
-  </si>
-  <si>
-    <t>workspace16</t>
-  </si>
-  <si>
-    <t>workspace17</t>
-  </si>
-  <si>
-    <t>workspace18</t>
-  </si>
-  <si>
-    <t>workspace19</t>
-  </si>
-  <si>
-    <t>workspace20</t>
-  </si>
-  <si>
-    <t>workspace21</t>
-  </si>
-  <si>
-    <t>workspace22</t>
-  </si>
-  <si>
-    <t>workspace23</t>
-  </si>
-  <si>
-    <t>workspace24</t>
-  </si>
-  <si>
-    <t>workspace25</t>
-  </si>
-  <si>
-    <t>workspace26</t>
-  </si>
-  <si>
-    <t>workspace27</t>
-  </si>
-  <si>
-    <t>workspace28</t>
-  </si>
-  <si>
-    <t>workspace29</t>
-  </si>
-  <si>
-    <t>workspace30</t>
-  </si>
-  <si>
-    <t>workspace31</t>
-  </si>
-  <si>
-    <t>workspace32</t>
-  </si>
-  <si>
-    <t>workspace33</t>
-  </si>
-  <si>
-    <t>workspace34</t>
+    <t>Pod 1</t>
+  </si>
+  <si>
+    <t>Pod 2</t>
+  </si>
+  <si>
+    <t>Pod 3</t>
+  </si>
+  <si>
+    <t>Pod 4</t>
+  </si>
+  <si>
+    <t>Pod 5</t>
+  </si>
+  <si>
+    <t>Pod 6</t>
+  </si>
+  <si>
+    <t>Pod 7</t>
+  </si>
+  <si>
+    <t>Pod 8</t>
+  </si>
+  <si>
+    <t>Pod 9</t>
+  </si>
+  <si>
+    <t>Pod 10</t>
+  </si>
+  <si>
+    <t>Pod 11</t>
+  </si>
+  <si>
+    <t>Pod 12</t>
+  </si>
+  <si>
+    <t>Pod 13</t>
+  </si>
+  <si>
+    <t>Pod 14</t>
+  </si>
+  <si>
+    <t>Pod 15</t>
+  </si>
+  <si>
+    <t>Pod 16</t>
+  </si>
+  <si>
+    <t>Pod 17</t>
+  </si>
+  <si>
+    <t>Pod 18</t>
+  </si>
+  <si>
+    <t>Pod 19</t>
+  </si>
+  <si>
+    <t>Pod 20</t>
+  </si>
+  <si>
+    <t>Pod 21</t>
+  </si>
+  <si>
+    <t>Pod 22</t>
+  </si>
+  <si>
+    <t>Pod 23</t>
+  </si>
+  <si>
+    <t>Pod 24</t>
+  </si>
+  <si>
+    <t>Pod 25</t>
+  </si>
+  <si>
+    <t>Pod 26</t>
+  </si>
+  <si>
+    <t>Pod 27</t>
+  </si>
+  <si>
+    <t>Pod 28</t>
+  </si>
+  <si>
+    <t>Pod 29</t>
+  </si>
+  <si>
+    <t>Pod 30</t>
+  </si>
+  <si>
+    <t>Pod 31</t>
+  </si>
+  <si>
+    <t>Pod 32</t>
+  </si>
+  <si>
+    <t>Pod 33</t>
+  </si>
+  <si>
+    <t>Pod 34</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -571,6 +571,10 @@
       <color rgb="FF202124"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Carlito"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1576,6 +1580,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter>&amp;R_x000D_&amp;1#&amp;"Aptos"&amp;8&amp;K000000 Cisco Confidential</oddFooter>
